--- a/resources/templates/standard/B1100-06.xlsx
+++ b/resources/templates/standard/B1100-06.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>폐기 보고서</t>
   </si>
@@ -679,12 +682,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -698,30 +703,30 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -796,7 +801,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -814,7 +819,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -834,7 +839,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -852,7 +857,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -872,7 +877,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -890,7 +895,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -910,7 +915,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -928,7 +933,7 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
@@ -948,7 +953,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -966,7 +971,7 @@
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -1600,7 +1605,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -1622,7 +1627,7 @@
       <c r="S27" s="17"/>
       <c r="T27" s="17"/>
       <c r="U27" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
@@ -1658,7 +1663,7 @@
       <c r="S28" s="20"/>
       <c r="T28" s="21"/>
       <c r="U28" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
@@ -1666,12 +1671,12 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
       <c r="AA28" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
       <c r="AD28" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE28" s="9"/>
       <c r="AF28" s="9"/>
